--- a/book_final.xlsx
+++ b/book_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ayans\Code\AutoquestV2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A630E5-E08C-4D11-8E62-476FBB730678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2828A7C1-A512-41BC-B047-E91F7A35C452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5415" uniqueCount="3490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5415" uniqueCount="3491">
   <si>
     <t>GBS locations and function information sourced through SSON</t>
   </si>
@@ -10661,6 +10661,9 @@
   </si>
   <si>
     <t>1943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a </t>
   </si>
 </sst>
 </file>
@@ -11775,7 +11778,7 @@
         <v>58</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>59</v>
+        <v>3490</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>60</v>
@@ -31089,7 +31092,7 @@
     <hyperlink ref="AF5" r:id="rId1" location=":~:text=The Delhi-based,Germany and China." display="200" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="D6" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="D7" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="D8" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="D8" r:id="rId4" display="Software Development" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
     <hyperlink ref="D9" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
     <hyperlink ref="D10" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
     <hyperlink ref="D11" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
